--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/OKLAHOMA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/OKLAHOMA_2014.xlsx
@@ -2454,7 +2454,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C117">
@@ -2580,7 +2580,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C124">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Gral. Simon Boivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C173">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C270">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C278">
@@ -11310,7 +11310,7 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C609">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="B682" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C682">
@@ -17034,7 +17034,7 @@
       </c>
       <c r="B927" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C927">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B1025" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1025">
